--- a/notebooks/XGBoost/predictions_afr_2019.xlsx
+++ b/notebooks/XGBoost/predictions_afr_2019.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>СКР_прогноз</t>
+          <t>predictions</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>СКР_реальный</t>
+          <t>СКР</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -470,16 +470,16 @@
         <v>2019</v>
       </c>
       <c r="C2" t="n">
-        <v>1.589138150215149</v>
+        <v>1.589476943016052</v>
       </c>
       <c r="D2" t="n">
         <v>1.47</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.119138150215149</v>
+        <v>-0.1194769430160523</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.104636069057753</v>
+        <v>-8.127683198370903</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         <v>2019</v>
       </c>
       <c r="C3" t="n">
-        <v>1.653576254844666</v>
+        <v>1.648353219032288</v>
       </c>
       <c r="D3" t="n">
         <v>1.524</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1295762548446655</v>
+        <v>-0.1243532190322876</v>
       </c>
       <c r="F3" t="n">
-        <v>-8.502378926815322</v>
+        <v>-8.159660041488687</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         <v>2019</v>
       </c>
       <c r="C4" t="n">
-        <v>1.703173041343689</v>
+        <v>1.686764478683472</v>
       </c>
       <c r="D4" t="n">
         <v>1.608</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.09517304134368887</v>
+        <v>-0.07876447868347158</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.918721476597566</v>
+        <v>-4.898288475340273</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         <v>2019</v>
       </c>
       <c r="C5" t="n">
-        <v>1.742584943771362</v>
+        <v>1.741871237754822</v>
       </c>
       <c r="D5" t="n">
         <v>1.666</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.07658494377136238</v>
+        <v>-0.07587123775482185</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.59693540044192</v>
+        <v>-4.554095903650772</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         <v>2019</v>
       </c>
       <c r="C6" t="n">
-        <v>1.374247908592224</v>
+        <v>1.364437818527222</v>
       </c>
       <c r="D6" t="n">
         <v>1.287</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0872479085922242</v>
+        <v>-0.07743781852722176</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.779169276785098</v>
+        <v>-6.016924516489648</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         <v>2019</v>
       </c>
       <c r="C7" t="n">
-        <v>1.418630838394165</v>
+        <v>1.411157965660095</v>
       </c>
       <c r="D7" t="n">
         <v>1.319</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.09963083839416509</v>
+        <v>-0.09215796566009526</v>
       </c>
       <c r="F7" t="n">
-        <v>-7.553513145880599</v>
+        <v>-6.986957214563705</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         <v>2019</v>
       </c>
       <c r="C8" t="n">
-        <v>1.431888103485107</v>
+        <v>1.43493127822876</v>
       </c>
       <c r="D8" t="n">
         <v>1.324</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1078881034851074</v>
+        <v>-0.1109312782287597</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.148648299479406</v>
+        <v>-8.378495334498465</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         <v>2019</v>
       </c>
       <c r="C9" t="n">
-        <v>1.367498517036438</v>
+        <v>1.367566347122192</v>
       </c>
       <c r="D9" t="n">
         <v>1.239</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1284985170364379</v>
+        <v>-0.1285663471221923</v>
       </c>
       <c r="F9" t="n">
-        <v>-10.37114746056803</v>
+        <v>-10.37662204376047</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         <v>2019</v>
       </c>
       <c r="C10" t="n">
-        <v>1.611058115959167</v>
+        <v>1.611923217773438</v>
       </c>
       <c r="D10" t="n">
         <v>1.512</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.09905811595916747</v>
+        <v>-0.09992321777343749</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.551462695712135</v>
+        <v>-6.608678424169145</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         <v>2019</v>
       </c>
       <c r="C11" t="n">
-        <v>1.307960987091064</v>
+        <v>1.306817054748535</v>
       </c>
       <c r="D11" t="n">
         <v>1.257</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.05096098709106456</v>
+        <v>-0.04981705474853526</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.054175584014683</v>
+        <v>-3.963170624386258</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         <v>2019</v>
       </c>
       <c r="C12" t="n">
-        <v>1.84117603302002</v>
+        <v>1.827208518981934</v>
       </c>
       <c r="D12" t="n">
         <v>1.707</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1341760330200195</v>
+        <v>-0.1202085189819335</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.860341711776184</v>
+        <v>-7.042092500406182</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         <v>2019</v>
       </c>
       <c r="C13" t="n">
-        <v>1.830482244491577</v>
+        <v>1.833800435066223</v>
       </c>
       <c r="D13" t="n">
         <v>1.762</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.06848224449157714</v>
+        <v>-0.07180043506622313</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.88662000519734</v>
+        <v>-4.074939561079633</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         <v>2019</v>
       </c>
       <c r="C14" t="n">
-        <v>1.51611602306366</v>
+        <v>1.523078322410583</v>
       </c>
       <c r="D14" t="n">
         <v>1.374</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1421160230636596</v>
+        <v>-0.1490783224105834</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.34323311962588</v>
+        <v>-10.84995068490418</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         <v>2019</v>
       </c>
       <c r="C15" t="n">
-        <v>1.874040365219116</v>
+        <v>1.863285899162292</v>
       </c>
       <c r="D15" t="n">
         <v>1.758</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1160403652191162</v>
+        <v>-0.1052858991622925</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.600703368550409</v>
+        <v>-5.988958996717433</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         <v>2019</v>
       </c>
       <c r="C16" t="n">
-        <v>1.550243377685547</v>
+        <v>1.558992028236389</v>
       </c>
       <c r="D16" t="n">
         <v>1.436</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1142433776855469</v>
+        <v>-0.1229920282363892</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.955666969745609</v>
+        <v>-8.564904473286157</v>
       </c>
     </row>
     <row r="17">
@@ -800,16 +800,16 @@
         <v>2019</v>
       </c>
       <c r="C17" t="n">
-        <v>1.511577725410461</v>
+        <v>1.521640300750732</v>
       </c>
       <c r="D17" t="n">
         <v>1.375</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1365777254104614</v>
+        <v>-0.1466403007507324</v>
       </c>
       <c r="F17" t="n">
-        <v>-9.932925484397193</v>
+        <v>-10.66474914550781</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         <v>2019</v>
       </c>
       <c r="C18" t="n">
-        <v>1.523474335670471</v>
+        <v>1.531342625617981</v>
       </c>
       <c r="D18" t="n">
         <v>1.359</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1644743356704712</v>
+        <v>-0.172342625617981</v>
       </c>
       <c r="F18" t="n">
-        <v>-12.10260012291915</v>
+        <v>-12.6815765723312</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         <v>2019</v>
       </c>
       <c r="C19" t="n">
-        <v>1.687684059143066</v>
+        <v>1.678790330886841</v>
       </c>
       <c r="D19" t="n">
         <v>1.665</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.02268405914306637</v>
+        <v>-0.01379033088684078</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.362405954538521</v>
+        <v>-0.8282481013117589</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         <v>2019</v>
       </c>
       <c r="C20" t="n">
-        <v>1.394303560256958</v>
+        <v>1.394696593284607</v>
       </c>
       <c r="D20" t="n">
         <v>1.423</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02869643974304203</v>
+        <v>0.02830340671539311</v>
       </c>
       <c r="F20" t="n">
-        <v>2.016615582785807</v>
+        <v>1.988995552733177</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         <v>2019</v>
       </c>
       <c r="C21" t="n">
-        <v>1.484975934028625</v>
+        <v>1.490864753723145</v>
       </c>
       <c r="D21" t="n">
         <v>1.389</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.09597593402862548</v>
+        <v>-0.1018647537231445</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.909714472903201</v>
+        <v>-7.333675574020483</v>
       </c>
     </row>
     <row r="22">
@@ -910,16 +910,16 @@
         <v>2019</v>
       </c>
       <c r="C22" t="n">
-        <v>1.729560732841492</v>
+        <v>1.727713823318481</v>
       </c>
       <c r="D22" t="n">
         <v>1.609</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1205607328414917</v>
+        <v>-0.1187138233184815</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.492898249937335</v>
+        <v>-7.378112076972124</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         <v>2019</v>
       </c>
       <c r="C23" t="n">
-        <v>1.76230776309967</v>
+        <v>1.758093118667603</v>
       </c>
       <c r="D23" t="n">
         <v>1.703</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.05930776309967034</v>
+        <v>-0.05509311866760247</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.482546277138599</v>
+        <v>-3.235062752061214</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         <v>2019</v>
       </c>
       <c r="C24" t="n">
-        <v>1.646544694900513</v>
+        <v>1.655434489250183</v>
       </c>
       <c r="D24" t="n">
         <v>1.608</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0385446949005126</v>
+        <v>-0.04743448925018301</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.397058140579142</v>
+        <v>-2.949906047896953</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>1.602273464202881</v>
+        <v>1.610089778900146</v>
       </c>
       <c r="D25" t="n">
         <v>1.495</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1072734642028808</v>
+        <v>-0.1150897789001464</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.175482555376639</v>
+        <v>-7.698312969909455</v>
       </c>
     </row>
     <row r="26">
@@ -998,16 +998,16 @@
         <v>2019</v>
       </c>
       <c r="C26" t="n">
-        <v>1.914514422416687</v>
+        <v>1.916543960571289</v>
       </c>
       <c r="D26" t="n">
         <v>1.786</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.128514422416687</v>
+        <v>-0.130543960571289</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.19565635031842</v>
+        <v>-7.30929230522335</v>
       </c>
     </row>
     <row r="27">
@@ -1020,16 +1020,16 @@
         <v>2019</v>
       </c>
       <c r="C27" t="n">
-        <v>1.438392043113708</v>
+        <v>1.432283759117126</v>
       </c>
       <c r="D27" t="n">
         <v>1.351</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.08739204311370852</v>
+        <v>-0.08128375911712649</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.468693050607587</v>
+        <v>-6.016562480912397</v>
       </c>
     </row>
     <row r="28">
@@ -1042,16 +1042,16 @@
         <v>2019</v>
       </c>
       <c r="C28" t="n">
-        <v>1.030644297599792</v>
+        <v>1.030293226242065</v>
       </c>
       <c r="D28" t="n">
         <v>0.981</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0496442975997925</v>
+        <v>-0.04929322624206545</v>
       </c>
       <c r="F28" t="n">
-        <v>-5.060580795085881</v>
+        <v>-5.024793704593828</v>
       </c>
     </row>
     <row r="29">
@@ -1064,16 +1064,16 @@
         <v>2019</v>
       </c>
       <c r="C29" t="n">
-        <v>1.422222375869751</v>
+        <v>1.432863473892212</v>
       </c>
       <c r="D29" t="n">
         <v>1.338</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0842223758697509</v>
+        <v>-0.09486347389221184</v>
       </c>
       <c r="F29" t="n">
-        <v>-6.29464692599035</v>
+        <v>-7.089945731854397</v>
       </c>
     </row>
     <row r="30">
@@ -1086,16 +1086,16 @@
         <v>2019</v>
       </c>
       <c r="C30" t="n">
-        <v>1.467297554016113</v>
+        <v>1.472673177719116</v>
       </c>
       <c r="D30" t="n">
         <v>1.377</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.09029755401611328</v>
+        <v>-0.09567317771911621</v>
       </c>
       <c r="F30" t="n">
-        <v>-6.557556573428706</v>
+        <v>-6.947943189478302</v>
       </c>
     </row>
     <row r="31">
@@ -1108,16 +1108,16 @@
         <v>2019</v>
       </c>
       <c r="C31" t="n">
-        <v>1.407378911972046</v>
+        <v>1.392524003982544</v>
       </c>
       <c r="D31" t="n">
         <v>1.233</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1743789119720458</v>
+        <v>-0.1595240039825438</v>
       </c>
       <c r="F31" t="n">
-        <v>-14.14265303909536</v>
+        <v>-12.93787542437501</v>
       </c>
     </row>
     <row r="32">
@@ -1130,16 +1130,16 @@
         <v>2019</v>
       </c>
       <c r="C32" t="n">
-        <v>1.588233113288879</v>
+        <v>1.589648008346558</v>
       </c>
       <c r="D32" t="n">
         <v>1.506</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.08223311328887939</v>
+        <v>-0.08364800834655761</v>
       </c>
       <c r="F32" t="n">
-        <v>-5.460366088239003</v>
+        <v>-5.554316623277398</v>
       </c>
     </row>
     <row r="33">
@@ -1152,16 +1152,16 @@
         <v>2019</v>
       </c>
       <c r="C33" t="n">
-        <v>2.14387035369873</v>
+        <v>2.14379096031189</v>
       </c>
       <c r="D33" t="n">
         <v>2.073</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.07087035369873051</v>
+        <v>-0.07079096031188969</v>
       </c>
       <c r="F33" t="n">
-        <v>-3.418733897671516</v>
+        <v>-3.414904018904472</v>
       </c>
     </row>
     <row r="34">
@@ -1174,16 +1174,16 @@
         <v>2019</v>
       </c>
       <c r="C34" t="n">
-        <v>1.507814049720764</v>
+        <v>1.514473915100098</v>
       </c>
       <c r="D34" t="n">
         <v>1.389</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1188140497207641</v>
+        <v>-0.1254739151000976</v>
       </c>
       <c r="F34" t="n">
-        <v>-8.55392726571376</v>
+        <v>-9.033399215269808</v>
       </c>
     </row>
     <row r="35">
@@ -1196,16 +1196,16 @@
         <v>2019</v>
       </c>
       <c r="C35" t="n">
-        <v>1.557531356811523</v>
+        <v>1.572874069213867</v>
       </c>
       <c r="D35" t="n">
         <v>1.443</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.1145313568115234</v>
+        <v>-0.1298740692138671</v>
       </c>
       <c r="F35" t="n">
-        <v>-7.937030964069534</v>
+        <v>-9.00028199680299</v>
       </c>
     </row>
     <row r="36">
@@ -1218,16 +1218,16 @@
         <v>2019</v>
       </c>
       <c r="C36" t="n">
-        <v>1.60112988948822</v>
+        <v>1.599087715148926</v>
       </c>
       <c r="D36" t="n">
         <v>1.506</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.09512988948822021</v>
+        <v>-0.09308771514892578</v>
       </c>
       <c r="F36" t="n">
-        <v>-6.316725729629496</v>
+        <v>-6.181123183859613</v>
       </c>
     </row>
     <row r="37">
@@ -1240,16 +1240,16 @@
         <v>2019</v>
       </c>
       <c r="C37" t="n">
-        <v>1.669772982597351</v>
+        <v>1.670656442642212</v>
       </c>
       <c r="D37" t="n">
         <v>1.555</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.1147729825973511</v>
+        <v>-0.115656442642212</v>
       </c>
       <c r="F37" t="n">
-        <v>-7.380899202402002</v>
+        <v>-7.437713353196912</v>
       </c>
     </row>
     <row r="38">
@@ -1262,16 +1262,16 @@
         <v>2019</v>
       </c>
       <c r="C38" t="n">
-        <v>1.748878002166748</v>
+        <v>1.744278192520142</v>
       </c>
       <c r="D38" t="n">
         <v>1.624</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.1248780021667479</v>
+        <v>-0.1202781925201415</v>
       </c>
       <c r="F38" t="n">
-        <v>-7.689532153124873</v>
+        <v>-7.406292642865855</v>
       </c>
     </row>
     <row r="39">
@@ -1284,16 +1284,16 @@
         <v>2019</v>
       </c>
       <c r="C39" t="n">
-        <v>1.380333065986633</v>
+        <v>1.390807271003723</v>
       </c>
       <c r="D39" t="n">
         <v>1.279</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.1013330659866334</v>
+        <v>-0.1118072710037232</v>
       </c>
       <c r="F39" t="n">
-        <v>-7.922835495436543</v>
+        <v>-8.741772556976017</v>
       </c>
     </row>
     <row r="40">
@@ -1306,16 +1306,16 @@
         <v>2019</v>
       </c>
       <c r="C40" t="n">
-        <v>1.358057141304016</v>
+        <v>1.349549531936646</v>
       </c>
       <c r="D40" t="n">
         <v>1.274</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.08405714130401609</v>
+        <v>-0.07554953193664549</v>
       </c>
       <c r="F40" t="n">
-        <v>-6.597891782104874</v>
+        <v>-5.930104547617384</v>
       </c>
     </row>
     <row r="41">
@@ -1328,16 +1328,16 @@
         <v>2019</v>
       </c>
       <c r="C41" t="n">
-        <v>1.727623701095581</v>
+        <v>1.725594639778137</v>
       </c>
       <c r="D41" t="n">
         <v>1.589</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.1386237010955811</v>
+        <v>-0.1365946397781372</v>
       </c>
       <c r="F41" t="n">
-        <v>-8.72395853339088</v>
+        <v>-8.596264303218202</v>
       </c>
     </row>
     <row r="42">
@@ -1350,16 +1350,16 @@
         <v>2019</v>
       </c>
       <c r="C42" t="n">
-        <v>1.561567068099976</v>
+        <v>1.561541318893433</v>
       </c>
       <c r="D42" t="n">
         <v>1.46</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1015670680999756</v>
+        <v>-0.1015413188934327</v>
       </c>
       <c r="F42" t="n">
-        <v>-6.95664849999833</v>
+        <v>-6.954884855714566</v>
       </c>
     </row>
     <row r="43">
@@ -1372,16 +1372,16 @@
         <v>2019</v>
       </c>
       <c r="C43" t="n">
-        <v>1.558056116104126</v>
+        <v>1.557186126708984</v>
       </c>
       <c r="D43" t="n">
         <v>1.474</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.084056116104126</v>
+        <v>-0.0831861267089844</v>
       </c>
       <c r="F43" t="n">
-        <v>-5.702585895802307</v>
+        <v>-5.643563548777775</v>
       </c>
     </row>
     <row r="44">
@@ -1394,16 +1394,16 @@
         <v>2019</v>
       </c>
       <c r="C44" t="n">
-        <v>1.367140412330627</v>
+        <v>1.367085814476013</v>
       </c>
       <c r="D44" t="n">
         <v>1.253</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.1141404123306275</v>
+        <v>-0.1140858144760133</v>
       </c>
       <c r="F44" t="n">
-        <v>-9.109370497256789</v>
+        <v>-9.105013126577278</v>
       </c>
     </row>
     <row r="45">
@@ -1416,16 +1416,16 @@
         <v>2019</v>
       </c>
       <c r="C45" t="n">
-        <v>2.482540130615234</v>
+        <v>2.445731639862061</v>
       </c>
       <c r="D45" t="n">
         <v>2.185</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.2975401306152343</v>
+        <v>-0.2607316398620605</v>
       </c>
       <c r="F45" t="n">
-        <v>-13.61739728216175</v>
+        <v>-11.93279816302336</v>
       </c>
     </row>
     <row r="46">
@@ -1438,16 +1438,16 @@
         <v>2019</v>
       </c>
       <c r="C46" t="n">
-        <v>1.631676912307739</v>
+        <v>1.629608392715454</v>
       </c>
       <c r="D46" t="n">
         <v>1.497</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.1346769123077391</v>
+        <v>-0.132608392715454</v>
       </c>
       <c r="F46" t="n">
-        <v>-8.996453727971886</v>
+        <v>-8.858276066496593</v>
       </c>
     </row>
     <row r="47">
@@ -1460,16 +1460,16 @@
         <v>2019</v>
       </c>
       <c r="C47" t="n">
-        <v>2.022429466247559</v>
+        <v>2.025894641876221</v>
       </c>
       <c r="D47" t="n">
         <v>1.854</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.1684294662475585</v>
+        <v>-0.1718946418762206</v>
       </c>
       <c r="F47" t="n">
-        <v>-9.084652979911462</v>
+        <v>-9.271555656754078</v>
       </c>
     </row>
     <row r="48">
@@ -1482,16 +1482,16 @@
         <v>2019</v>
       </c>
       <c r="C48" t="n">
-        <v>1.85206151008606</v>
+        <v>1.861963510513306</v>
       </c>
       <c r="D48" t="n">
         <v>1.788</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.06406151008605954</v>
+        <v>-0.07396351051330563</v>
       </c>
       <c r="F48" t="n">
-        <v>-3.582858505931742</v>
+        <v>-4.136661661817988</v>
       </c>
     </row>
     <row r="49">
@@ -1504,16 +1504,16 @@
         <v>2019</v>
       </c>
       <c r="C49" t="n">
-        <v>1.938368558883667</v>
+        <v>1.937784433364868</v>
       </c>
       <c r="D49" t="n">
         <v>1.96</v>
       </c>
       <c r="E49" t="n">
-        <v>0.02163144111633297</v>
+        <v>0.0222155666351318</v>
       </c>
       <c r="F49" t="n">
-        <v>1.103644954914948</v>
+        <v>1.133447277302643</v>
       </c>
     </row>
     <row r="50">
@@ -1526,16 +1526,16 @@
         <v>2019</v>
       </c>
       <c r="C50" t="n">
-        <v>1.611374378204346</v>
+        <v>1.600762367248535</v>
       </c>
       <c r="D50" t="n">
         <v>1.537</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.07437437820434578</v>
+        <v>-0.06376236724853523</v>
       </c>
       <c r="F50" t="n">
-        <v>-4.838931568272335</v>
+        <v>-4.148494941349072</v>
       </c>
     </row>
     <row r="51">
@@ -1548,16 +1548,16 @@
         <v>2019</v>
       </c>
       <c r="C51" t="n">
-        <v>1.726434469223022</v>
+        <v>1.698974609375</v>
       </c>
       <c r="D51" t="n">
         <v>1.631</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.09543446922302246</v>
+        <v>-0.06797460937499999</v>
       </c>
       <c r="F51" t="n">
-        <v>-5.851285666647606</v>
+        <v>-4.167664584610669</v>
       </c>
     </row>
     <row r="52">
@@ -1570,16 +1570,16 @@
         <v>2019</v>
       </c>
       <c r="C52" t="n">
-        <v>1.699942469596863</v>
+        <v>1.682474493980408</v>
       </c>
       <c r="D52" t="n">
         <v>1.63</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0699424695968629</v>
+        <v>-0.05247449398040782</v>
       </c>
       <c r="F52" t="n">
-        <v>-4.290949055022264</v>
+        <v>-3.219294109227474</v>
       </c>
     </row>
     <row r="53">
@@ -1592,16 +1592,16 @@
         <v>2019</v>
       </c>
       <c r="C53" t="n">
-        <v>1.61472499370575</v>
+        <v>1.610547184944153</v>
       </c>
       <c r="D53" t="n">
         <v>1.546</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.06872499370574947</v>
+        <v>-0.06454718494415279</v>
       </c>
       <c r="F53" t="n">
-        <v>-4.445342413049771</v>
+        <v>-4.175108987332004</v>
       </c>
     </row>
     <row r="54">
@@ -1614,16 +1614,16 @@
         <v>2019</v>
       </c>
       <c r="C54" t="n">
-        <v>1.611525535583496</v>
+        <v>1.619653940200806</v>
       </c>
       <c r="D54" t="n">
         <v>1.496</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1155255355834961</v>
+        <v>-0.1236539402008057</v>
       </c>
       <c r="F54" t="n">
-        <v>-7.722295159324606</v>
+        <v>-8.265637713957599</v>
       </c>
     </row>
     <row r="55">
@@ -1636,16 +1636,16 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>1.262452244758606</v>
+        <v>1.261719703674316</v>
       </c>
       <c r="D55" t="n">
         <v>1.188</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.07445224475860601</v>
+        <v>-0.07371970367431646</v>
       </c>
       <c r="F55" t="n">
-        <v>-6.267023969579631</v>
+        <v>-6.20536226214785</v>
       </c>
     </row>
     <row r="56">
@@ -1658,16 +1658,16 @@
         <v>2019</v>
       </c>
       <c r="C56" t="n">
-        <v>1.849488496780396</v>
+        <v>1.841442704200745</v>
       </c>
       <c r="D56" t="n">
         <v>1.773</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0764884967803956</v>
+        <v>-0.06844270420074472</v>
       </c>
       <c r="F56" t="n">
-        <v>-4.31407201243066</v>
+        <v>-3.860276604666933</v>
       </c>
     </row>
     <row r="57">
@@ -1680,16 +1680,16 @@
         <v>2019</v>
       </c>
       <c r="C57" t="n">
-        <v>1.784744739532471</v>
+        <v>1.791828632354736</v>
       </c>
       <c r="D57" t="n">
         <v>1.71</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.07474473953247074</v>
+        <v>-0.08182863235473636</v>
       </c>
       <c r="F57" t="n">
-        <v>-4.371037399559692</v>
+        <v>-4.785300137703881</v>
       </c>
     </row>
     <row r="58">
@@ -1702,16 +1702,16 @@
         <v>2019</v>
       </c>
       <c r="C58" t="n">
-        <v>1.594245553016663</v>
+        <v>1.610142469406128</v>
       </c>
       <c r="D58" t="n">
         <v>1.52</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.07424555301666258</v>
+        <v>-0.09014246940612791</v>
       </c>
       <c r="F58" t="n">
-        <v>-4.88457585635938</v>
+        <v>-5.930425618824205</v>
       </c>
     </row>
     <row r="59">
@@ -1724,16 +1724,16 @@
         <v>2019</v>
       </c>
       <c r="C59" t="n">
-        <v>2.763979196548462</v>
+        <v>2.765125513076782</v>
       </c>
       <c r="D59" t="n">
         <v>2.559</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2049791965484618</v>
+        <v>-0.2061255130767821</v>
       </c>
       <c r="F59" t="n">
-        <v>-8.010128821745282</v>
+        <v>-8.054924309370147</v>
       </c>
     </row>
     <row r="60">
@@ -1746,16 +1746,16 @@
         <v>2019</v>
       </c>
       <c r="C60" t="n">
-        <v>1.723872780799866</v>
+        <v>1.709768414497375</v>
       </c>
       <c r="D60" t="n">
         <v>1.579</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.1448727807998658</v>
+        <v>-0.1307684144973755</v>
       </c>
       <c r="F60" t="n">
-        <v>-9.174970284981999</v>
+        <v>-8.281723527382871</v>
       </c>
     </row>
     <row r="61">
@@ -1768,16 +1768,16 @@
         <v>2019</v>
       </c>
       <c r="C61" t="n">
-        <v>1.410414576530457</v>
+        <v>1.409045100212097</v>
       </c>
       <c r="D61" t="n">
         <v>1.323</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.08741457653045659</v>
+        <v>-0.08604510021209721</v>
       </c>
       <c r="F61" t="n">
-        <v>-6.607299813337611</v>
+        <v>-6.503786864104098</v>
       </c>
     </row>
     <row r="62">
@@ -1790,16 +1790,16 @@
         <v>2019</v>
       </c>
       <c r="C62" t="n">
-        <v>1.440492510795593</v>
+        <v>1.42797577381134</v>
       </c>
       <c r="D62" t="n">
         <v>1.345</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.09549251079559329</v>
+        <v>-0.08297577381134036</v>
       </c>
       <c r="F62" t="n">
-        <v>-7.099814929040393</v>
+        <v>-6.169202513854303</v>
       </c>
     </row>
     <row r="63">
@@ -1812,16 +1812,16 @@
         <v>2019</v>
       </c>
       <c r="C63" t="n">
-        <v>1.513582348823547</v>
+        <v>1.509142398834229</v>
       </c>
       <c r="D63" t="n">
         <v>1.396</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.1175823488235475</v>
+        <v>-0.1131423988342286</v>
       </c>
       <c r="F63" t="n">
-        <v>-8.422804356987641</v>
+        <v>-8.104756363483427</v>
       </c>
     </row>
     <row r="64">
@@ -1834,16 +1834,16 @@
         <v>2019</v>
       </c>
       <c r="C64" t="n">
-        <v>1.309704422950745</v>
+        <v>1.311879873275757</v>
       </c>
       <c r="D64" t="n">
         <v>1.235</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.07470442295074453</v>
+        <v>-0.07687987327575674</v>
       </c>
       <c r="F64" t="n">
-        <v>-6.048941129614941</v>
+        <v>-6.22509095350257</v>
       </c>
     </row>
     <row r="65">
@@ -1856,16 +1856,16 @@
         <v>2019</v>
       </c>
       <c r="C65" t="n">
-        <v>1.897815346717834</v>
+        <v>1.898191928863525</v>
       </c>
       <c r="D65" t="n">
         <v>1.877</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.02081534671783447</v>
+        <v>-0.02119192886352539</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.108968924764756</v>
+        <v>-1.129031905355641</v>
       </c>
     </row>
     <row r="66">
@@ -1878,16 +1878,16 @@
         <v>2019</v>
       </c>
       <c r="C66" t="n">
-        <v>1.738131761550903</v>
+        <v>1.734008550643921</v>
       </c>
       <c r="D66" t="n">
         <v>1.614</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.1241317615509032</v>
+        <v>-0.1200085506439208</v>
       </c>
       <c r="F66" t="n">
-        <v>-7.690939377379381</v>
+        <v>-7.435474017591128</v>
       </c>
     </row>
     <row r="67">
@@ -1900,16 +1900,16 @@
         <v>2019</v>
       </c>
       <c r="C67" t="n">
-        <v>1.292011618614197</v>
+        <v>1.291604995727539</v>
       </c>
       <c r="D67" t="n">
         <v>1.234</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.05801161861419679</v>
+        <v>-0.05760499572753908</v>
       </c>
       <c r="F67" t="n">
-        <v>-4.701103615413031</v>
+        <v>-4.668152003852438</v>
       </c>
     </row>
     <row r="68">
@@ -1922,16 +1922,16 @@
         <v>2019</v>
       </c>
       <c r="C68" t="n">
-        <v>1.433449387550354</v>
+        <v>1.429676532745361</v>
       </c>
       <c r="D68" t="n">
         <v>1.348</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.08544938755035392</v>
+        <v>-0.08167653274536124</v>
       </c>
       <c r="F68" t="n">
-        <v>-6.338975337563346</v>
+        <v>-6.059089966273088</v>
       </c>
     </row>
     <row r="69">
@@ -1944,16 +1944,16 @@
         <v>2019</v>
       </c>
       <c r="C69" t="n">
-        <v>1.305492520332336</v>
+        <v>1.311299324035645</v>
       </c>
       <c r="D69" t="n">
         <v>1.283</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.02249252033233651</v>
+        <v>-0.02829932403564461</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.753119277656782</v>
+        <v>-2.205715045646502</v>
       </c>
     </row>
     <row r="70">
@@ -1966,16 +1966,16 @@
         <v>2019</v>
       </c>
       <c r="C70" t="n">
-        <v>1.49446177482605</v>
+        <v>1.493435740470886</v>
       </c>
       <c r="D70" t="n">
         <v>1.411</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.08346177482604977</v>
+        <v>-0.0824357404708862</v>
       </c>
       <c r="F70" t="n">
-        <v>-5.915079718359303</v>
+        <v>-5.842362896590092</v>
       </c>
     </row>
     <row r="71">
@@ -1988,16 +1988,16 @@
         <v>2019</v>
       </c>
       <c r="C71" t="n">
-        <v>1.430035352706909</v>
+        <v>1.416426301002502</v>
       </c>
       <c r="D71" t="n">
         <v>1.345</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.08503535270690921</v>
+        <v>-0.07142630100250247</v>
       </c>
       <c r="F71" t="n">
-        <v>-6.322331056275778</v>
+        <v>-5.310505650743678</v>
       </c>
     </row>
     <row r="72">
@@ -2010,16 +2010,16 @@
         <v>2019</v>
       </c>
       <c r="C72" t="n">
-        <v>1.296765804290771</v>
+        <v>1.307413101196289</v>
       </c>
       <c r="D72" t="n">
         <v>1.22</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.07676580429077151</v>
+        <v>-0.08741310119628909</v>
       </c>
       <c r="F72" t="n">
-        <v>-6.292279040227173</v>
+        <v>-7.165008294777794</v>
       </c>
     </row>
     <row r="73">
@@ -2032,16 +2032,16 @@
         <v>2019</v>
       </c>
       <c r="C73" t="n">
-        <v>1.812256336212158</v>
+        <v>1.818715214729309</v>
       </c>
       <c r="D73" t="n">
         <v>1.715</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.09725633621215812</v>
+        <v>-0.103715214729309</v>
       </c>
       <c r="F73" t="n">
-        <v>-5.670923394294934</v>
+        <v>-6.047534386548629</v>
       </c>
     </row>
     <row r="74">
@@ -2054,16 +2054,16 @@
         <v>2019</v>
       </c>
       <c r="C74" t="n">
-        <v>1.631586909294128</v>
+        <v>1.629067182540894</v>
       </c>
       <c r="D74" t="n">
         <v>1.494</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.1375869092941284</v>
+        <v>-0.1350671825408936</v>
       </c>
       <c r="F74" t="n">
-        <v>-9.20929781085197</v>
+        <v>-9.040641401666235</v>
       </c>
     </row>
     <row r="75">
@@ -2076,16 +2076,16 @@
         <v>2019</v>
       </c>
       <c r="C75" t="n">
-        <v>1.517634749412537</v>
+        <v>1.517537355422974</v>
       </c>
       <c r="D75" t="n">
         <v>1.425</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.09263474941253658</v>
+        <v>-0.09253735542297359</v>
       </c>
       <c r="F75" t="n">
-        <v>-6.500684169300812</v>
+        <v>-6.493849503366568</v>
       </c>
     </row>
     <row r="76">
@@ -2098,16 +2098,16 @@
         <v>2019</v>
       </c>
       <c r="C76" t="n">
-        <v>1.5809645652771</v>
+        <v>1.59053647518158</v>
       </c>
       <c r="D76" t="n">
         <v>1.564</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.01696456527709955</v>
+        <v>-0.02653647518157953</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.084690874494856</v>
+        <v>-1.696705574269791</v>
       </c>
     </row>
     <row r="77">
@@ -2120,16 +2120,16 @@
         <v>2019</v>
       </c>
       <c r="C77" t="n">
-        <v>1.793350100517273</v>
+        <v>1.785955309867859</v>
       </c>
       <c r="D77" t="n">
         <v>1.695</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.09835010051727289</v>
+        <v>-0.09095530986785882</v>
       </c>
       <c r="F77" t="n">
-        <v>-5.802365812228489</v>
+        <v>-5.366094977454797</v>
       </c>
     </row>
     <row r="78">
@@ -2142,16 +2142,16 @@
         <v>2019</v>
       </c>
       <c r="C78" t="n">
-        <v>1.567694664001465</v>
+        <v>1.56671679019928</v>
       </c>
       <c r="D78" t="n">
         <v>1.474</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.09369466400146487</v>
+        <v>-0.09271679019927981</v>
       </c>
       <c r="F78" t="n">
-        <v>-6.356490095079027</v>
+        <v>-6.290148588824954</v>
       </c>
     </row>
     <row r="79">
@@ -2164,16 +2164,16 @@
         <v>2019</v>
       </c>
       <c r="C79" t="n">
-        <v>2.631836175918579</v>
+        <v>2.636663436889648</v>
       </c>
       <c r="D79" t="n">
         <v>2.602</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.02983617591857923</v>
+        <v>-0.03466343688964857</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.146663179038403</v>
+        <v>-1.332184353944987</v>
       </c>
     </row>
     <row r="80">
@@ -2186,16 +2186,16 @@
         <v>2019</v>
       </c>
       <c r="C80" t="n">
-        <v>1.634454131126404</v>
+        <v>1.626046657562256</v>
       </c>
       <c r="D80" t="n">
         <v>1.495</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.1394541311264037</v>
+        <v>-0.1310466575622558</v>
       </c>
       <c r="F80" t="n">
-        <v>-9.328035526849746</v>
+        <v>-8.765662713194363</v>
       </c>
     </row>
     <row r="81">
@@ -2208,16 +2208,16 @@
         <v>2019</v>
       </c>
       <c r="C81" t="n">
-        <v>1.950154304504395</v>
+        <v>1.954401135444641</v>
       </c>
       <c r="D81" t="n">
         <v>1.617</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.3331543045043945</v>
+        <v>-0.3374011354446411</v>
       </c>
       <c r="F81" t="n">
-        <v>-20.60323466322786</v>
+        <v>-20.86587108501182</v>
       </c>
     </row>
     <row r="82">
@@ -2230,16 +2230,16 @@
         <v>2019</v>
       </c>
       <c r="C82" t="n">
-        <v>1.880288600921631</v>
+        <v>1.888131141662598</v>
       </c>
       <c r="D82" t="n">
         <v>1.805</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.07528860092163092</v>
+        <v>-0.08313114166259772</v>
       </c>
       <c r="F82" t="n">
-        <v>-4.171113624467087</v>
+        <v>-4.6056034162104</v>
       </c>
     </row>
     <row r="83">
@@ -2252,16 +2252,16 @@
         <v>2019</v>
       </c>
       <c r="C83" t="n">
-        <v>1.510518789291382</v>
+        <v>1.510309100151062</v>
       </c>
       <c r="D83" t="n">
         <v>1.395</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.1155187892913818</v>
+        <v>-0.115309100151062</v>
       </c>
       <c r="F83" t="n">
-        <v>-8.280916795081133</v>
+        <v>-8.265885315488315</v>
       </c>
     </row>
     <row r="84">
@@ -2274,16 +2274,16 @@
         <v>2019</v>
       </c>
       <c r="C84" t="n">
-        <v>1.379601120948792</v>
+        <v>1.374082088470459</v>
       </c>
       <c r="D84" t="n">
         <v>1.43</v>
       </c>
       <c r="E84" t="n">
-        <v>0.05039887905120843</v>
+        <v>0.05591791152954095</v>
       </c>
       <c r="F84" t="n">
-        <v>3.524397136448142</v>
+        <v>3.910343463604263</v>
       </c>
     </row>
     <row r="85">
@@ -2296,16 +2296,16 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>1.438130259513855</v>
+        <v>1.441208124160767</v>
       </c>
       <c r="D85" t="n">
         <v>1.35</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.08813025951385489</v>
+        <v>-0.09120812416076651</v>
       </c>
       <c r="F85" t="n">
-        <v>-6.528167371396658</v>
+        <v>-6.756157345241963</v>
       </c>
     </row>
     <row r="86">
@@ -2318,16 +2318,16 @@
         <v>2019</v>
       </c>
       <c r="C86" t="n">
-        <v>1.247748017311096</v>
+        <v>1.250165462493896</v>
       </c>
       <c r="D86" t="n">
         <v>1.136</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.1117480173110963</v>
+        <v>-0.1141654624938966</v>
       </c>
       <c r="F86" t="n">
-        <v>-9.836973354850025</v>
+        <v>-10.04977662798386</v>
       </c>
     </row>
   </sheetData>
